--- a/ci-cd-merge-resolver/repoCollector/datasets/chunjun.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/chunjun.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="95">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -51,6 +51,252 @@
   </si>
   <si>
     <t>7ae9b0f4bb5985252bf7b00f86422e290776da20</t>
+  </si>
+  <si>
+    <t>4a731815e7b259000af3242bb1e3740451058f63</t>
+  </si>
+  <si>
+    <t>c22513dfc8e2c521f5dd4554f48ec094e4e6486e</t>
+  </si>
+  <si>
+    <t>d4722c31d65293af685fdb22b5b8dc1ea45ec742</t>
+  </si>
+  <si>
+    <t>10450e7df9c51e3e5bb79c3a84891b32dfb20ea5</t>
+  </si>
+  <si>
+    <t>989467b71486950b86867905d2aacafb292ff7b9</t>
+  </si>
+  <si>
+    <t>711ea197780a6d46b635df4e30b8d9c0fcdf61ea</t>
+  </si>
+  <si>
+    <t>86eb522b60e2a09dd285330f23b0430707eeca51</t>
+  </si>
+  <si>
+    <t>218a7bc08ee83d1d9b98cbd232ea3440ce753149</t>
+  </si>
+  <si>
+    <t>81144369e2b7b918710a1030f557a2b8712e3c3b</t>
+  </si>
+  <si>
+    <t>e2a141611fbeb69f7926ccc3f62d1faf93bf8743</t>
+  </si>
+  <si>
+    <t>f7b32f54016f9574e2543b147602df07c4e0bf85</t>
+  </si>
+  <si>
+    <t>0beb4a71f6bd9cd2ad2252734e0679c6b7c637e3</t>
+  </si>
+  <si>
+    <t>cbd6fcbb1ce0b72895a911299601d795f8d4e72b</t>
+  </si>
+  <si>
+    <t>a2faa327ce82a65a5b0b88a3c70ab35ada6a1af2</t>
+  </si>
+  <si>
+    <t>760c788b6d063132a52ef02b73f6d6d195627353</t>
+  </si>
+  <si>
+    <t>70d1309b5c7c65a06cfce3c3114486fd4f0b0f5f</t>
+  </si>
+  <si>
+    <t>5f8f532cc2f18a6fdbf8223f331d84507d322756</t>
+  </si>
+  <si>
+    <t>c5244bda2748172d455d443905d92d5b78ccbf8d</t>
+  </si>
+  <si>
+    <t>3c5bd58e8f6b7182182694b590b1ff3003af4012</t>
+  </si>
+  <si>
+    <t>991b21fb6e0a9c0d7b5034c18053f5e980ed492e</t>
+  </si>
+  <si>
+    <t>55b3c44b98b7447a276233d7fca33cd64ca2ec1b</t>
+  </si>
+  <si>
+    <t>111512d06d9eef54971296f45c1adf50b0944002</t>
+  </si>
+  <si>
+    <t>75e3ddc8ebc89cf136ea58b6fa27bb97727f0f82</t>
+  </si>
+  <si>
+    <t>c4433687883e4cfd4a8d9fbc1500f2ba5e61491e</t>
+  </si>
+  <si>
+    <t>cbc4516dec54b6793639c3d7bc4d687906fc985e</t>
+  </si>
+  <si>
+    <t>d0033242e9d23307dbcc8388e97382b62416ce1e</t>
+  </si>
+  <si>
+    <t>61f8ad3cff047d7ed544684a144897b968b0752b</t>
+  </si>
+  <si>
+    <t>762c2d40e7c0553114d3ff6578ed9608a5aa3750</t>
+  </si>
+  <si>
+    <t>4d231ff2554c642d40903a42853b08dc31367200</t>
+  </si>
+  <si>
+    <t>93ba96f859b949f0a6ec315b3c0f8b3a4a954b2e</t>
+  </si>
+  <si>
+    <t>84173921edd114aedc0f39f24118283578332ecc</t>
+  </si>
+  <si>
+    <t>8cac480223a586aa9c1cc3b87361319a6f6880cb</t>
+  </si>
+  <si>
+    <t>4026837c0fb67f67f6cba2eec97277d612f6ad1a</t>
+  </si>
+  <si>
+    <t>e2617b0b4ae6581322017ab9e572f204291d6820</t>
+  </si>
+  <si>
+    <t>a853a713af1a8d82022c0578352e88865faa215b</t>
+  </si>
+  <si>
+    <t>a6bc6a4212acf840ed771df6e7163bc38d0a87aa</t>
+  </si>
+  <si>
+    <t>5b870e7d994a961d9fcd9226d16e75cf9fee399c</t>
+  </si>
+  <si>
+    <t>c622c456bf13cb3399aef2d5fa8d5ab0af15dd6c</t>
+  </si>
+  <si>
+    <t>566a2d9392fd6154bc3597f6a8417406351c8bba</t>
+  </si>
+  <si>
+    <t>ced86756600664e4c86b1228305b5711569cbacb</t>
+  </si>
+  <si>
+    <t>32ab352fd26409282d035d35a9c99566b5b86e29</t>
+  </si>
+  <si>
+    <t>3abb127c3afd52b8e748ad917f994a31a7c9c1d2</t>
+  </si>
+  <si>
+    <t>f6bcf3819566605c62a10b2886cad1f164e9ac97</t>
+  </si>
+  <si>
+    <t>0c025a1133d21271a98b47ef9395819c3a879154</t>
+  </si>
+  <si>
+    <t>0f2ddf1887889a70dcf478d87a334c2acba135f8</t>
+  </si>
+  <si>
+    <t>69a6a81aa9790f236b74b282697078b3392e3548</t>
+  </si>
+  <si>
+    <t>9fae26a4e13187e31c999b5511be7faaf32f95ad</t>
+  </si>
+  <si>
+    <t>02aae2e6e50482efcb45c4b640a6ec64b60f5c76</t>
+  </si>
+  <si>
+    <t>63ef05357092beef9f40feda59d7ebe520537ff1</t>
+  </si>
+  <si>
+    <t>df4a8ee77a2519ea932eb6e33fc50e3a82463404</t>
+  </si>
+  <si>
+    <t>a13b258b2771dd73e89ce0c79075510729d3b3a9</t>
+  </si>
+  <si>
+    <t>5e8557791f10a67020bbb47be4d19696895152cc</t>
+  </si>
+  <si>
+    <t>97ca8e25de14c2cf3977876137a3bb1502b11fbe</t>
+  </si>
+  <si>
+    <t>33d651732afc7061d1a794cedb628eff47266ead</t>
+  </si>
+  <si>
+    <t>30a598891342787fbbe8ee4503621239f25e9cd8</t>
+  </si>
+  <si>
+    <t>d6ab98b7740c6849a1dccd469ff20caff29e7a7e</t>
+  </si>
+  <si>
+    <t>753413b75a5c1ab6f08b25af859421c1cc290e40</t>
+  </si>
+  <si>
+    <t>56cf268d852d78c2dd9420569cc14a986c270d37</t>
+  </si>
+  <si>
+    <t>ea84b0486f875eff6779a3da541ff00ddd65152e</t>
+  </si>
+  <si>
+    <t>6b7055256373a3d45573c3e30fcdfab1f9ef5273</t>
+  </si>
+  <si>
+    <t>f7e98ecc42904dfcb8c3dbb69c4751c3180fc029</t>
+  </si>
+  <si>
+    <t>c169bab705df1a12baa7037381d818a24563e5a8</t>
+  </si>
+  <si>
+    <t>e5309f92cf7e32f451dd3d33dbc44f26f6a28b3c</t>
+  </si>
+  <si>
+    <t>b717dd2e8f4c34c94378e7e37f131c66b1126ba6</t>
+  </si>
+  <si>
+    <t>4e68ce5cdc1fbad644b26b6a660ea3bd1f510afa</t>
+  </si>
+  <si>
+    <t>a9ed6f634afe67f94d85ac94abd968207947eb08</t>
+  </si>
+  <si>
+    <t>cb6a69d6cce97bfc6212a8c28e39178d52261b05</t>
+  </si>
+  <si>
+    <t>d7f4fc2d0dbd12930663b0f7e751e9d03b89ec97</t>
+  </si>
+  <si>
+    <t>effb3c4a8b3ff9f3e7a2c3f252ff7e660c523b48</t>
+  </si>
+  <si>
+    <t>33c7784fe8f0215915d515ca5211c1d8ab9e5f1d</t>
+  </si>
+  <si>
+    <t>e698c041e5c1492061eb47e8871fb3fdda228e28</t>
+  </si>
+  <si>
+    <t>f58ff4846923a86bd0d4dea2edcb5db6119e6223</t>
+  </si>
+  <si>
+    <t>07e1305903961c7fdccb588866e9803d69c40afc</t>
+  </si>
+  <si>
+    <t>4f4b454b36ba192320b6c8ed6acd53fcb4ffff99</t>
+  </si>
+  <si>
+    <t>81ba7d83fffa8d159ee7e8f139aa394918fd8e08</t>
+  </si>
+  <si>
+    <t>d11ac7ebf7258ea29d1ce43dafe9cfa7a8aa66bd</t>
+  </si>
+  <si>
+    <t>63520cf9c74840479e09d724812b1010215b4861</t>
+  </si>
+  <si>
+    <t>b7881d87a5f611be7ef1eff93cb71efa8a464af9</t>
+  </si>
+  <si>
+    <t>93cb154a0229d0df18f54280de686fe4678823b1</t>
+  </si>
+  <si>
+    <t>1ce25449ed3f5c1eea8f4337b41fbe3ef692f6d8</t>
+  </si>
+  <si>
+    <t>892f5e8dcd91232df6716600405bccd6abaaac9b</t>
+  </si>
+  <si>
+    <t>f92d58594d92b731ef894a0f6e6948acc4126a90</t>
   </si>
 </sst>
 </file>
@@ -95,7 +341,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -141,25 +387,985 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G2" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H2" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n" s="0">
+        <v>1.4789998531341553</v>
+      </c>
+      <c r="J2" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G3" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>0.5929999947547913</v>
+      </c>
+      <c r="J3" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G4" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>0.5540000200271606</v>
+      </c>
+      <c r="J4" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="F5" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="G5" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n" s="0">
+        <v>0.6119999885559082</v>
+      </c>
+      <c r="J5" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="G6" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n" s="0">
+        <v>0.28200000524520874</v>
+      </c>
+      <c r="J6" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="D7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G7" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n" s="0">
+        <v>0.44699999690055847</v>
+      </c>
+      <c r="J7" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="D8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G8" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H8" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>0.6330000162124634</v>
+      </c>
+      <c r="J8" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F9" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G9" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H9" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>0.6290000081062317</v>
+      </c>
+      <c r="J9" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D10" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E10" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F10" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G10" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H10" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>0.3779999911785126</v>
+      </c>
+      <c r="J10" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D11" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E11" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F11" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G11" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H11" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>0.4779999852180481</v>
+      </c>
+      <c r="J11" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="D12" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E12" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F12" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G12" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n" s="0">
+        <v>0.210999995470047</v>
+      </c>
+      <c r="J12" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="D13" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E13" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F13" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G13" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>0.18400000035762787</v>
+      </c>
+      <c r="J13" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D14" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E14" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F14" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G14" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H14" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n" s="0">
+        <v>0.1459999978542328</v>
+      </c>
+      <c r="J14" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="D15" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E15" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F15" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G15" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H15" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n" s="0">
+        <v>394.5610046386719</v>
+      </c>
+      <c r="J15" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="D16" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E16" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F16" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G16" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H16" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n" s="0">
+        <v>392.7049865722656</v>
+      </c>
+      <c r="J16" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E17" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F17" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G17" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H17" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n" s="0">
+        <v>393.2820129394531</v>
+      </c>
+      <c r="J17" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="D18" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E18" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F18" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="G18" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H18" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n" s="0">
+        <v>392.8320007324219</v>
+      </c>
+      <c r="J18" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="D19" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E19" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F19" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G19" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H19" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n" s="0">
+        <v>393.61602783203125</v>
+      </c>
+      <c r="J19" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="D20" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E20" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F20" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G20" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n" s="0">
+        <v>393.64501953125</v>
+      </c>
+      <c r="J20" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="D21" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E21" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F21" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G21" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n" s="0">
+        <v>394.17901611328125</v>
+      </c>
+      <c r="J21" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="D22" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E22" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F22" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G22" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n" s="0">
+        <v>393.6679992675781</v>
+      </c>
+      <c r="J22" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D23" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E23" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F23" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G23" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H23" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n" s="0">
+        <v>392.17498779296875</v>
+      </c>
+      <c r="J23" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="D24" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E24" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F24" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G24" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H24" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n" s="0">
+        <v>393.1579895019531</v>
+      </c>
+      <c r="J24" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="D25" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E25" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F25" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G25" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H25" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n" s="0">
+        <v>393.8249816894531</v>
+      </c>
+      <c r="J25" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="D26" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E26" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F26" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G26" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H26" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n" s="0">
+        <v>392.5169982910156</v>
+      </c>
+      <c r="J26" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="D27" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E27" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="F27" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="G27" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H27" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n" s="0">
+        <v>394.26800537109375</v>
+      </c>
+      <c r="J27" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="D28" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E28" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F28" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G28" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H28" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n" s="0">
+        <v>392.77398681640625</v>
+      </c>
+      <c r="J28" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="D29" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E29" t="n" s="0">
         <v>10.0</v>
       </c>
-      <c r="E2" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="F2" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G2" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H2" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n" s="0">
-        <v>0.6470000147819519</v>
-      </c>
-      <c r="J2" t="b" s="0">
-        <v>1</v>
+      <c r="F29" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="G29" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H29" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n" s="0">
+        <v>392.16400146484375</v>
+      </c>
+      <c r="J29" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="D30" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E30" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F30" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G30" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H30" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n" s="0">
+        <v>392.0469970703125</v>
+      </c>
+      <c r="J30" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="D31" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E31" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F31" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G31" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H31" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n" s="0">
+        <v>391.7829895019531</v>
+      </c>
+      <c r="J31" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="D32" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E32" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F32" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G32" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H32" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n" s="0">
+        <v>392.66802978515625</v>
+      </c>
+      <c r="J32" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
